--- a/events/Vaires_2023_WC/Vaires_2023_WC_start.xlsx
+++ b/events/Vaires_2023_WC/Vaires_2023_WC_start.xlsx
@@ -36323,6 +36323,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X608" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -43456,6 +43461,11 @@
       <c r="R713" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X713" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>

--- a/events/Vaires_2023_WC/Vaires_2023_WC_start.xlsx
+++ b/events/Vaires_2023_WC/Vaires_2023_WC_start.xlsx
@@ -50396,12 +50396,12 @@
       </c>
       <c r="M815" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R815" t="inlineStr">
@@ -50474,12 +50474,12 @@
       </c>
       <c r="M816" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R816" t="inlineStr">
@@ -50552,12 +50552,12 @@
       </c>
       <c r="M817" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R817" t="inlineStr">
@@ -50630,12 +50630,12 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R818" t="inlineStr">
@@ -50708,12 +50708,12 @@
       </c>
       <c r="M819" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R819" t="inlineStr">
@@ -50786,12 +50786,12 @@
       </c>
       <c r="M820" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R820" t="inlineStr">
@@ -50864,12 +50864,12 @@
       </c>
       <c r="M821" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R821" t="inlineStr">
@@ -50942,12 +50942,12 @@
       </c>
       <c r="M822" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R822" t="inlineStr">
